--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_901_Sicily_Italy.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_901_Sicily_Italy.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf71c01a65310432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd596e97b8cfc46e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra742a7208dbb46cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R264f88692cec4691"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd5f3f324497340f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R30ccc58d22e14e24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc301f70f9216480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re26c724ca2a64720"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rbe77e298c5ef43c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6728a048f9554b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5eb06793c9e148cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1d7b9f01ba0a4279"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ901CommercialTable" displayName="EEZ901CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ901CommercialTable" displayName="EEZ901CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ901FunctionalTable" displayName="EEZ901FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ901FunctionalTable" displayName="EEZ901FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ901ValidationTable" displayName="EEZ901ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ901ValidationTable" displayName="EEZ901ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10878,7 +10832,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29f2b30151d2461c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88943ad22cd94446"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10888,20 +10842,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10909,714 +10853,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3656.648435608</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3656.648435608</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$153,A2,'Species'!$U$2:$U$153))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>471067.57078714046</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>471067.57078714046</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>151.1835167781</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.178958635705795</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1509.9363337201653</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>151.1835167781</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1594.482646276086</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$153,A3,'Species'!$U$2:$U$153))</x:f>
-        <x:v>241059.49390566992</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.178958635705795</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1509.9363337201653</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>228277.48504284542</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>12782.0088628245</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0559932963184058</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.055993296318405834</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>6448.110253182599</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.286527053448835</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>193.43143488548054</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>6448.110253182599</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>200.2113901689049</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$153,A4,'Species'!$U$2:$U$153))</x:f>
-        <x:v>1290985.1177520575</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.286527053448835</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>193.43143488548054</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1247267.2185728895</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>43717.899179168046</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0350509486084223</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0350509486084222</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>351.53818273099995</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.7159231452866774</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>519.9039838347632</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>351.53818273099995</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>730.3263214200887</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$153,A5,'Species'!$U$2:$U$153))</x:f>
-        <x:v>256737.58783263413</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.7159231452866774</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>519.9039838347632</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>182766.10167187982</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>73971.48616075431</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.4047330740443071</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.4047330740443072</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>174.6844359811</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.343320097105896</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>220.45507303292612</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>174.6844359811</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>229.5544555652427</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$153,A6,'Species'!$U$2:$U$153))</x:f>
-        <x:v>40099.590597362905</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.343320097105896</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>220.45507303292612</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>38510.07009192891</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1589.5205054339967</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0412754508532338</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.041275450853233704</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>35.454447429</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.2007741691655176</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>15.877209274170587</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>35.454447429</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>23.32024485119555</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$153,A7,'Species'!$U$2:$U$153))</x:f>
-        <x:v>826.8063951081206</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.2007741691655176</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>15.877209274170587</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>562.9176815303123</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>263.8887135778083</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.4687873950955266</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.4687873950955265</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>10309.0672932079</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5034159243280247</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>318.72484921042025</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>10309.0672932079</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>466.96952115665584</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$153,A8,'Species'!$U$2:$U$153))</x:f>
-        <x:v>4814020.217481035</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5034159243280247</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>318.72484921042025</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3285755.918527763</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1528264.298953272</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4651180236291064</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4651180236291063</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>13404.381902239296</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4287562713821718</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>268.3837837358275</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>13404.381902239296</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>538.5158995936021</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$153,A9,'Species'!$U$2:$U$153))</x:f>
-        <x:v>7218472.778580594</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4287562713821718</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>268.3837837358275</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3597518.733563031</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3620954.045017563</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.006514298656986</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.006514298656986</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>12.945473633</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>12.945473633</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$153,A10,'Species'!$U$2:$U$153))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2898.1305470976185</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>2898.1305470976185</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>845.5751485521001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.907977397279973</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>809.0537911319675</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>845.5751485521001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>888.5148576526619</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$153,A11,'Species'!$U$2:$U$153))</x:f>
-        <x:v>751306.0827503977</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.907977397279973</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>809.0537911319675</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>684115.7796230532</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>67190.30312734458</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0982148126511075</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0982148126511076</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>207.9120086221</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.8423490729058787</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>695.5831819019269</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>207.9120086221</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>815.7332883994303</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$153,A12,'Species'!$U$2:$U$153))</x:f>
-        <x:v>169600.74649103632</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.8423490729058787</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>695.5831819019269</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>144620.09651298117</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>24980.649978055153</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1727329090519094</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.17273290905190952</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3971.0544506827005</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.462419597193688</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2900.1442328074227</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3971.0544506827005</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2961.2420032637083</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$153,A13,'Species'!$U$2:$U$153))</x:f>
-        <x:v>11759253.236608904</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.462419597193688</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2900.1442328074227</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>11516630.66331168</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>242622.57329722308</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0210671489249143</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.021067148924914417</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b5bf37da3af499f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc59ce63f3104975"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11626,20 +11106,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11647,1416 +11117,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3234.0982996583</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.814176790028926</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>651.893709091015</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3234.0982996583</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>723.5720556667571</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$153,A2,'Species'!$U$2:$U$153))</x:f>
-        <x:v>2340103.15491212</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.814176790028926</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>651.893709091015</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2108288.336129194</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>231814.81878292607</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.109954039402664</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.10995403940266388</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>539.1231577628</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.827904436888064</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>672.8285893134384</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>539.1231577628</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>686.5698573864425</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$153,A3,'Species'!$U$2:$U$153))</x:f>
-        <x:v>370145.70953893417</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.827904436888064</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>672.8285893134384</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>362737.47370375105</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>7408.235835183121</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0204231334566591</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.020423133456659217</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>159.42015392099998</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.8817942460506707</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>761.7180484314315</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>159.42015392099998</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2437.4401953034157</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$153,A4,'Species'!$U$2:$U$153))</x:f>
-        <x:v>388577.09110850276</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.8817942460506707</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>761.7180484314315</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>121433.20852534253</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>267143.88258316024</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>3.199924434405508</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>2.199924434405508</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>299.88539200300005</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.034809926586171</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1083.4526261372325</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>299.88539200300005</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1305.7434817188475</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$153,A5,'Species'!$U$2:$U$153))</x:f>
-        <x:v>391573.3958706187</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.034809926586171</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1083.4526261372325</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>324911.61550584383</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>66661.78036477487</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2051689665233771</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.20516896652337716</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>32.874466262</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>32.874466262</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$153,A6,'Species'!$U$2:$U$153))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>75311.05136162134</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>75311.05136162134</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3994.6457240354002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.457562505557812</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2867.890105143811</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3994.6457240354002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2921.476336562386</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$153,A7,'Species'!$U$2:$U$153))</x:f>
-        <x:v>11670262.955719542</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.457562505557812</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2867.890105143811</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>11456204.94551616</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>214058.010203382</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0186848970685674</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01868489706856738</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>119.66340844289999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.887329379188363</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>771.4883622260356</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>119.66340844289999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>884.1542603778186</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$153,A8,'Species'!$U$2:$U$153))</x:f>
-        <x:v>105800.91238612105</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.887329379188363</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>771.4883622260356</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>92318.92699799807</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>13481.98538812298</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1460370676580256</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.14603706765802568</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>394.93384781270004</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.271662076138108</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1869.2271316410527</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>394.93384781270004</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2230.4241526173155</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$153,A9,'Species'!$U$2:$U$153))</x:f>
-        <x:v>880869.9928475373</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.271662076138108</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1869.2271316410527</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>738221.0635348973</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>142648.92931264</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1932333502238204</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1932333502238204</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>52.92662634820001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8513674180256046</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>710.1783327575437</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>52.92662634820001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>854.7148811081709</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$153,A10,'Species'!$U$2:$U$153))</x:f>
-        <x:v>45237.17514665835</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8513674180256046</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>710.1783327575437</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>37587.34325844616</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7649.831888212189</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2035214842297537</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.2035214842297537</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>385.271176742</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.970770372388456</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>93.49112211791228</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>385.271176742</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>107.15215401714134</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$153,A11,'Species'!$U$2:$U$153))</x:f>
-        <x:v>41282.63646862407</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.970770372388456</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>93.49112211791228</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>36019.43463329809</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5263.201835325977</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1461211673339375</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.14612116733393757</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>263.57763264600004</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.2159712493137596</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1644.2628679275692</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>263.57763264600004</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2225.6821203213517</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$153,A12,'Species'!$U$2:$U$153))</x:f>
-        <x:v>586640.0242968317</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.2159712493137596</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1644.2628679275692</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>433390.91417607135</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>153249.11012076034</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3536048059800825</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3536048059800826</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>13.9281939904</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>13.9281939904</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$153,A13,'Species'!$U$2:$U$153))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>16745.372273109908</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>16745.372273109908</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>2933.6609399433</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.299821289086122</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>199.44414392455303</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>2933.6609399433</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>320.4857713210111</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$153,A14,'Species'!$U$2:$U$153))</x:f>
-        <x:v>940196.5891320509</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.299821289086122</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>199.44414392455303</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>585101.4947318911</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>355095.0944001598</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.6068948679799113</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.6068948679799112</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>9603.755085626097</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.244489314297725</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>175.5857691247843</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>9603.755085626097</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>242.49938575059625</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$153,A15,'Species'!$U$2:$U$153))</x:f>
-        <x:v>2328904.7091634935</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.244489314297725</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>175.5857691247843</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1686282.7231957167</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>642621.9859677767</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.3810879261989517</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.38108792619895177</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>5558.4068594214</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.6428833204485924</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>439.42354202918966</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>5558.4068594214</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>741.7759315908435</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$153,A16,'Species'!$U$2:$U$153))</x:f>
-        <x:v>4123092.4263082435</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.6428833204485924</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>439.42354202918966</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2442494.830206296</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1680597.5961019476</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.6880659788172416</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.6880659788172417</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>99.4935948502</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.71973017362265</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>524.4814995922949</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>99.4935948502</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>621.351976988938</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$153,A17,'Species'!$U$2:$U$153))</x:f>
-        <x:v>61820.54185790819</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.71973017362265</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>524.4814995922949</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>52182.54982686112</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>9637.99203104707</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.1846976060584506</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.1846976060584507</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>88.3307203491</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0861106880114724</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>12.193003206498435</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>88.3307203491</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>15.529759073626712</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$153,A18,'Species'!$U$2:$U$153))</x:f>
-        <x:v>1371.7548058214195</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0861106880114724</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>12.193003206498435</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1077.016756448893</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>294.7380493725266</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2736615262554762</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.27366152625547624</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>6062.8390764405995</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.306592231914318</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>202.57797797060877</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>6062.8390764405995</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>206.12496316117213</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$153,A19,'Species'!$U$2:$U$153))</x:f>
-        <x:v>1249702.4812834335</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.306592231914318</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>202.57797797060877</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1228197.6808665297</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>21504.800416903803</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.017509233856989</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.017509233856989156</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>390.7866658411</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.404056562073493</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>253.54588245849058</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>390.7866658411</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>258.0767646416222</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$153,A20,'Species'!$U$2:$U$153))</x:f>
-        <x:v>100852.95838535782</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.404056562073493</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>253.54588245849058</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>99082.35004369298</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>1770.608341664847</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.017870068088656</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.017870068088656058</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>834.6901221703001</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.4871542650605605</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>307.01123245064815</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>834.6901221703001</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>590.6379614158601</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$153,A21,'Species'!$U$2:$U$153))</x:f>
-        <x:v>492999.67217262124</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.4871542650605605</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>307.01123245064815</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>256259.24312188593</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>236740.4290507353</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.9238317657019428</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.9238317657019428</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>3936.4758313771</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.1227576690669916</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>132.66539946938985</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>3936.4758313771</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>134.08724455960223</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$153,A22,'Species'!$U$2:$U$153))</x:f>
-        <x:v>527831.1975048247</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.1227576690669916</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>132.66539946938985</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>522234.13867124147</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>5597.058833583258</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0107175276741276</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.010717527674127671</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>215.78288270299998</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.4564333002395315</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>286.04430146911574</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>215.78288270299998</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>356.9159925525324</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$153,A23,'Species'!$U$2:$U$153))</x:f>
-        <x:v>77016.3617557879</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.4564333002395315</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>286.04430146911574</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>61723.463951771766</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>15292.897804016138</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.2477647368586668</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.24776473685866682</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>318.66371646899995</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.649477918748098</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>446.14694012645447</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>318.66371646899995</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>569.3354062437234</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$153,A24,'Species'!$U$2:$U$153))</x:f>
-        <x:v>181426.53647101278</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.649477918748098</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>446.14694012645447</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>142170.84203196838</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>39255.6944390444</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.2761163532408242</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.2761163532408242</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>22.205293505</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.5722764050886613</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>373.4877870651328</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>22.205293505</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>400.36317124596496</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$153,A25,'Species'!$U$2:$U$153))</x:f>
-        <x:v>8890.18172610923</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.5722764050886613</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>373.4877870651328</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>8293.405932314217</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>596.7757937950119</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0719578661246703</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.07195786612467017</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>13.116680326000001</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.852811743959094</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>712.5440927279947</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>13.116680326000001</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>737.4180807757311</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$153,A26,'Species'!$U$2:$U$153))</x:f>
-        <x:v>9672.477232147712</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.852811743959094</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>712.5440927279947</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>9346.213082492808</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>326.26414965490403</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0349087001093584</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.03490870010935845</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8a5610cd348402b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64a4aa069ce54ca8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13231,7 +11782,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13330,7 +11881,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>27016327.359729037</x:v>
+        <x:v>21399990.68593382</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13344,7 +11895,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>27016327.359729033</x:v>
+        <x:v>22897615.638034843</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13358,7 +11909,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-5616336.673795216</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13372,7 +11923,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-4118711.721694194</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13383,9 +11934,9 @@
         <x:v>EEZ_901</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13397,47 +11948,19 @@
         <x:v>EEZ_901</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_901</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_901</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5326dfc545784b2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Race0e345f8b4410c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13484,7 +12007,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
